--- a/inst/extdata/bulkshift_example_sample_sheet.xlsx
+++ b/inst/extdata/bulkshift_example_sample_sheet.xlsx
@@ -255,7 +255,7 @@
         <v>26</v>
       </c>
       <c r="S2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
